--- a/astro-site/public/dl/bar-checklist-templates/08-venue-opening-closing-checklist.xlsx
+++ b/astro-site/public/dl/bar-checklist-templates/08-venue-opening-closing-checklist.xlsx
@@ -1040,13 +1040,13 @@
       <c r="G7" s="19" t="inlineStr"/>
       <c r="H7" s="20" t="inlineStr"/>
     </row>
-    <row r="8" ht="24" customHeight="1">
+    <row r="8" ht="47" customHeight="1">
       <c r="A8" s="21" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Raise security gate and open front door</t>
+          <t>Raise security gate and open front door; check every emergency exit is unlocked and clear and the exit signs are lit</t>
         </is>
       </c>
       <c r="C8" s="19" t="inlineStr">
@@ -1973,17 +1973,17 @@
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>Set the alarm</t>
+          <t>Clean the beer faucets</t>
         </is>
       </c>
       <c r="C16" s="19" t="inlineStr">
         <is>
-          <t>Entrance</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
         <is>
-          <t>Shift manager</t>
+          <t>Last one out</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -2001,12 +2001,12 @@
       </c>
       <c r="B17" s="18" t="inlineStr">
         <is>
-          <t>Lock up and verify it is locked</t>
+          <t>Empty and clean the garnish station</t>
         </is>
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
-          <t>Entrance</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
@@ -2029,17 +2029,17 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>Clean the beer faucets</t>
+          <t>Set the alarm</t>
         </is>
       </c>
       <c r="C18" s="19" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Entrance</t>
         </is>
       </c>
       <c r="D18" s="19" t="inlineStr">
         <is>
-          <t>Last one out</t>
+          <t>Shift manager</t>
         </is>
       </c>
       <c r="E18" s="19" t="inlineStr">
@@ -2057,12 +2057,12 @@
       </c>
       <c r="B19" s="18" t="inlineStr">
         <is>
-          <t>Empty and clean the garnish station</t>
+          <t>Lock up and verify it is locked</t>
         </is>
       </c>
       <c r="C19" s="19" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Entrance</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
